--- a/analises/vinhos/tanyno-brancos-agosto-2026.xlsx
+++ b/analises/vinhos/tanyno-brancos-agosto-2026.xlsx
@@ -1,17 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12768"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Vinhos Brancos" state="visible" r:id="rId4"/>
+    <sheet name="Vinhos Brancos" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vinhos Brancos'!$A$1:$H$112</definedName>
+  </definedNames>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="199">
   <si>
     <t>Linha</t>
   </si>
@@ -605,6 +611,9 @@
   </si>
   <si>
     <t>RUMO LUMINA</t>
+  </si>
+  <si>
+    <t>VENDA</t>
   </si>
 </sst>
 </file>
@@ -612,18 +621,20 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;R$&quot; #,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -669,7 +680,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -679,44 +690,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -746,12 +757,12 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -790,220 +801,164 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H112"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:L112"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="42" customWidth="1"/>
-    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="14" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="6" max="6" width="20" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="14" style="1" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="10" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="0" hidden="1" customWidth="1"/>
+    <col min="11" max="12" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1028,8 +983,11 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J1" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1049,13 +1007,13 @@
         <v>13</v>
       </c>
       <c r="G2" s="1">
-        <v>727.23525</v>
+        <v>727.23524999999995</v>
       </c>
       <c r="H2">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1075,13 +1033,28 @@
         <v>18</v>
       </c>
       <c r="G3" s="1">
-        <v>76.98885</v>
+        <v>76.988849999999999</v>
       </c>
       <c r="H3">
         <v>2836</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3" s="1">
+        <f>G3*1.13</f>
+        <v>86.997400499999998</v>
+      </c>
+      <c r="J3">
+        <v>110</v>
+      </c>
+      <c r="K3">
+        <f>J3*0.92</f>
+        <v>101.2</v>
+      </c>
+      <c r="L3" s="1">
+        <f>K3/I3</f>
+        <v>1.1632531480064165</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1101,13 +1074,13 @@
         <v>18</v>
       </c>
       <c r="G4" s="1">
-        <v>271.67085</v>
+        <v>271.67084999999997</v>
       </c>
       <c r="H4">
         <v>290</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1127,13 +1100,13 @@
         <v>18</v>
       </c>
       <c r="G5" s="1">
-        <v>271.67085</v>
+        <v>271.67084999999997</v>
       </c>
       <c r="H5">
         <v>215</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1153,13 +1126,13 @@
         <v>18</v>
       </c>
       <c r="G6" s="1">
-        <v>271.67085</v>
+        <v>271.67084999999997</v>
       </c>
       <c r="H6">
         <v>283</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -1179,13 +1152,28 @@
         <v>27</v>
       </c>
       <c r="G7" s="1">
-        <v>79.67265</v>
+        <v>79.672650000000004</v>
       </c>
       <c r="H7">
         <v>173</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I7" s="1">
+        <f>G7*1.13</f>
+        <v>90.03009449999999</v>
+      </c>
+      <c r="J7">
+        <v>120</v>
+      </c>
+      <c r="K7">
+        <f>J7*0.92</f>
+        <v>110.4</v>
+      </c>
+      <c r="L7" s="1">
+        <f>K7/I7</f>
+        <v>1.226256626888246</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -1205,13 +1193,13 @@
         <v>27</v>
       </c>
       <c r="G8" s="1">
-        <v>158.58915</v>
+        <v>158.58914999999999</v>
       </c>
       <c r="H8">
         <v>697</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -1231,13 +1219,13 @@
         <v>31</v>
       </c>
       <c r="G9" s="1">
-        <v>107.85255</v>
+        <v>107.85254999999999</v>
       </c>
       <c r="H9">
         <v>281</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1263,7 +1251,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -1289,7 +1277,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -1309,13 +1297,13 @@
         <v>40</v>
       </c>
       <c r="G12" s="1">
-        <v>812.1903</v>
+        <v>812.19029999999998</v>
       </c>
       <c r="H12">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -1335,13 +1323,13 @@
         <v>40</v>
       </c>
       <c r="G13" s="1">
-        <v>812.1903</v>
+        <v>812.19029999999998</v>
       </c>
       <c r="H13">
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -1361,13 +1349,13 @@
         <v>44</v>
       </c>
       <c r="G14" s="1">
-        <v>272.8743</v>
+        <v>272.87430000000001</v>
       </c>
       <c r="H14">
         <v>68</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -1387,13 +1375,13 @@
         <v>47</v>
       </c>
       <c r="G15" s="1">
-        <v>449.33415</v>
+        <v>449.33415000000002</v>
       </c>
       <c r="H15">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -1413,13 +1401,13 @@
         <v>47</v>
       </c>
       <c r="G16" s="1">
-        <v>422.30445</v>
+        <v>422.30444999999997</v>
       </c>
       <c r="H16">
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -1439,13 +1427,13 @@
         <v>36</v>
       </c>
       <c r="G17" s="1">
-        <v>314.388</v>
+        <v>314.38799999999998</v>
       </c>
       <c r="H17">
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>8</v>
       </c>
@@ -1471,7 +1459,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>8</v>
       </c>
@@ -1491,13 +1479,13 @@
         <v>40</v>
       </c>
       <c r="G19" s="1">
-        <v>266.037</v>
+        <v>266.03699999999998</v>
       </c>
       <c r="H19">
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -1523,7 +1511,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -1543,13 +1531,13 @@
         <v>58</v>
       </c>
       <c r="G21" s="1">
-        <v>151.23</v>
+        <v>151.22999999999999</v>
       </c>
       <c r="H21">
         <v>443</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -1569,13 +1557,13 @@
         <v>58</v>
       </c>
       <c r="G22" s="1">
-        <v>357.78675</v>
+        <v>357.78674999999998</v>
       </c>
       <c r="H22">
         <v>90</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -1595,13 +1583,13 @@
         <v>55</v>
       </c>
       <c r="G23" s="1">
-        <v>549.35895</v>
+        <v>549.35895000000005</v>
       </c>
       <c r="H23">
         <v>68</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>8</v>
       </c>
@@ -1627,7 +1615,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>8</v>
       </c>
@@ -1653,7 +1641,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>8</v>
       </c>
@@ -1679,7 +1667,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>8</v>
       </c>
@@ -1705,7 +1693,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>8</v>
       </c>
@@ -1725,13 +1713,13 @@
         <v>55</v>
       </c>
       <c r="G28" s="1">
-        <v>284.98335</v>
+        <v>284.98334999999997</v>
       </c>
       <c r="H28">
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>8</v>
       </c>
@@ -1757,7 +1745,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>8</v>
       </c>
@@ -1783,7 +1771,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>8</v>
       </c>
@@ -1809,7 +1797,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>8</v>
       </c>
@@ -1829,13 +1817,13 @@
         <v>55</v>
       </c>
       <c r="G32" s="1">
-        <v>291.9165</v>
+        <v>291.91649999999998</v>
       </c>
       <c r="H32">
         <v>80</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>8</v>
       </c>
@@ -1855,13 +1843,13 @@
         <v>55</v>
       </c>
       <c r="G33" s="1">
-        <v>229.188</v>
+        <v>229.18799999999999</v>
       </c>
       <c r="H33">
         <v>174</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>8</v>
       </c>
@@ -1881,13 +1869,13 @@
         <v>55</v>
       </c>
       <c r="G34" s="1">
-        <v>304.9095</v>
+        <v>304.90949999999998</v>
       </c>
       <c r="H34">
         <v>86</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>8</v>
       </c>
@@ -1913,7 +1901,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>8</v>
       </c>
@@ -1933,13 +1921,13 @@
         <v>55</v>
       </c>
       <c r="G36" s="1">
-        <v>266.676</v>
+        <v>266.67599999999999</v>
       </c>
       <c r="H36">
         <v>87</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>8</v>
       </c>
@@ -1959,13 +1947,13 @@
         <v>55</v>
       </c>
       <c r="G37" s="1">
-        <v>266.676</v>
+        <v>266.67599999999999</v>
       </c>
       <c r="H37">
         <v>46</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>8</v>
       </c>
@@ -1985,13 +1973,13 @@
         <v>55</v>
       </c>
       <c r="G38" s="1">
-        <v>1400.80515</v>
+        <v>1400.8051499999999</v>
       </c>
       <c r="H38">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>8</v>
       </c>
@@ -2011,13 +1999,13 @@
         <v>55</v>
       </c>
       <c r="G39" s="1">
-        <v>582.7466999999999</v>
+        <v>582.74669999999992</v>
       </c>
       <c r="H39">
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>8</v>
       </c>
@@ -2037,13 +2025,13 @@
         <v>55</v>
       </c>
       <c r="G40" s="1">
-        <v>284.98335</v>
+        <v>284.98334999999997</v>
       </c>
       <c r="H40">
         <v>238</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>8</v>
       </c>
@@ -2069,7 +2057,7 @@
         <v>1489</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>8</v>
       </c>
@@ -2089,13 +2077,13 @@
         <v>55</v>
       </c>
       <c r="G42" s="1">
-        <v>703.5922499999999</v>
+        <v>703.59224999999992</v>
       </c>
       <c r="H42">
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>8</v>
       </c>
@@ -2115,13 +2103,13 @@
         <v>55</v>
       </c>
       <c r="G43" s="1">
-        <v>750.8782499999999</v>
+        <v>750.87824999999987</v>
       </c>
       <c r="H43">
         <v>124</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>8</v>
       </c>
@@ -2147,7 +2135,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>22</v>
       </c>
@@ -2173,7 +2161,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>22</v>
       </c>
@@ -2199,7 +2187,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>8</v>
       </c>
@@ -2225,7 +2213,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>8</v>
       </c>
@@ -2245,13 +2233,13 @@
         <v>55</v>
       </c>
       <c r="G48" s="1">
-        <v>6398.3922</v>
+        <v>6398.3922000000002</v>
       </c>
       <c r="H48">
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>8</v>
       </c>
@@ -2271,13 +2259,13 @@
         <v>99</v>
       </c>
       <c r="G49" s="1">
-        <v>129.3762</v>
+        <v>129.37620000000001</v>
       </c>
       <c r="H49">
         <v>37</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>8</v>
       </c>
@@ -2303,7 +2291,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>8</v>
       </c>
@@ -2329,7 +2317,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>8</v>
       </c>
@@ -2349,13 +2337,13 @@
         <v>105</v>
       </c>
       <c r="G52" s="1">
-        <v>192.9354</v>
+        <v>192.93539999999999</v>
       </c>
       <c r="H52">
         <v>150</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>8</v>
       </c>
@@ -2381,7 +2369,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>8</v>
       </c>
@@ -2407,7 +2395,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>8</v>
       </c>
@@ -2433,7 +2421,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>8</v>
       </c>
@@ -2459,7 +2447,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>8</v>
       </c>
@@ -2485,7 +2473,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>8</v>
       </c>
@@ -2505,13 +2493,13 @@
         <v>58</v>
       </c>
       <c r="G58" s="1">
-        <v>315.20805</v>
+        <v>315.20805000000001</v>
       </c>
       <c r="H58">
         <v>94</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>8</v>
       </c>
@@ -2537,7 +2525,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>8</v>
       </c>
@@ -2563,7 +2551,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>8</v>
       </c>
@@ -2583,13 +2571,13 @@
         <v>58</v>
       </c>
       <c r="G61" s="1">
-        <v>255.1527</v>
+        <v>255.15270000000001</v>
       </c>
       <c r="H61">
         <v>147</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>8</v>
       </c>
@@ -2609,13 +2597,13 @@
         <v>55</v>
       </c>
       <c r="G62" s="1">
-        <v>189.3996</v>
+        <v>189.39959999999999</v>
       </c>
       <c r="H62">
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>8</v>
       </c>
@@ -2635,13 +2623,13 @@
         <v>55</v>
       </c>
       <c r="G63" s="1">
-        <v>228.5277</v>
+        <v>228.52770000000001</v>
       </c>
       <c r="H63">
         <v>6</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>8</v>
       </c>
@@ -2667,7 +2655,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>8</v>
       </c>
@@ -2687,13 +2675,13 @@
         <v>55</v>
       </c>
       <c r="G65" s="1">
-        <v>186.30045</v>
+        <v>186.30045000000001</v>
       </c>
       <c r="H65">
         <v>513</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>8</v>
       </c>
@@ -2713,13 +2701,13 @@
         <v>55</v>
       </c>
       <c r="G66" s="1">
-        <v>155.2557</v>
+        <v>155.25569999999999</v>
       </c>
       <c r="H66">
         <v>38</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>8</v>
       </c>
@@ -2739,13 +2727,13 @@
         <v>55</v>
       </c>
       <c r="G67" s="1">
-        <v>315.71925</v>
+        <v>315.71924999999999</v>
       </c>
       <c r="H67">
         <v>30</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>8</v>
       </c>
@@ -2765,13 +2753,13 @@
         <v>55</v>
       </c>
       <c r="G68" s="1">
-        <v>750.8782499999999</v>
+        <v>750.87824999999987</v>
       </c>
       <c r="H68">
         <v>66</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>8</v>
       </c>
@@ -2797,7 +2785,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>8</v>
       </c>
@@ -2817,13 +2805,13 @@
         <v>55</v>
       </c>
       <c r="G70" s="1">
-        <v>1214.8881</v>
+        <v>1214.8880999999999</v>
       </c>
       <c r="H70">
         <v>7</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>8</v>
       </c>
@@ -2849,7 +2837,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>8</v>
       </c>
@@ -2869,13 +2857,13 @@
         <v>55</v>
       </c>
       <c r="G72" s="1">
-        <v>690.13065</v>
+        <v>690.13064999999995</v>
       </c>
       <c r="H72">
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>8</v>
       </c>
@@ -2895,13 +2883,13 @@
         <v>55</v>
       </c>
       <c r="G73" s="1">
-        <v>760.7294999999999</v>
+        <v>760.72949999999992</v>
       </c>
       <c r="H73">
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>8</v>
       </c>
@@ -2921,13 +2909,13 @@
         <v>55</v>
       </c>
       <c r="G74" s="1">
-        <v>760.7294999999999</v>
+        <v>760.72949999999992</v>
       </c>
       <c r="H74">
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>8</v>
       </c>
@@ -2947,13 +2935,13 @@
         <v>55</v>
       </c>
       <c r="G75" s="1">
-        <v>528.7085999999999</v>
+        <v>528.70859999999993</v>
       </c>
       <c r="H75">
         <v>64</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>8</v>
       </c>
@@ -2973,13 +2961,13 @@
         <v>55</v>
       </c>
       <c r="G76" s="1">
-        <v>530.4445499999999</v>
+        <v>530.44454999999994</v>
       </c>
       <c r="H76">
         <v>33</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>8</v>
       </c>
@@ -2999,13 +2987,13 @@
         <v>55</v>
       </c>
       <c r="G77" s="1">
-        <v>528.7085999999999</v>
+        <v>528.70859999999993</v>
       </c>
       <c r="H77">
         <v>49</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>8</v>
       </c>
@@ -3031,7 +3019,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>8</v>
       </c>
@@ -3051,13 +3039,13 @@
         <v>55</v>
       </c>
       <c r="G79" s="1">
-        <v>203.2446</v>
+        <v>203.24459999999999</v>
       </c>
       <c r="H79">
         <v>28</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>8</v>
       </c>
@@ -3083,7 +3071,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>8</v>
       </c>
@@ -3109,7 +3097,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>8</v>
       </c>
@@ -3135,7 +3123,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>8</v>
       </c>
@@ -3155,13 +3143,13 @@
         <v>58</v>
       </c>
       <c r="G83" s="1">
-        <v>348.4893</v>
+        <v>348.48930000000001</v>
       </c>
       <c r="H83">
         <v>78</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>8</v>
       </c>
@@ -3181,13 +3169,13 @@
         <v>58</v>
       </c>
       <c r="G84" s="1">
-        <v>354.99645</v>
+        <v>354.99644999999998</v>
       </c>
       <c r="H84">
         <v>63</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>8</v>
       </c>
@@ -3207,13 +3195,13 @@
         <v>58</v>
       </c>
       <c r="G85" s="1">
-        <v>348.4893</v>
+        <v>348.48930000000001</v>
       </c>
       <c r="H85">
         <v>85</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>8</v>
       </c>
@@ -3239,7 +3227,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>8</v>
       </c>
@@ -3265,7 +3253,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>8</v>
       </c>
@@ -3291,7 +3279,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>8</v>
       </c>
@@ -3317,7 +3305,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>22</v>
       </c>
@@ -3343,7 +3331,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>8</v>
       </c>
@@ -3363,13 +3351,13 @@
         <v>161</v>
       </c>
       <c r="G91" s="1">
-        <v>358.53225</v>
+        <v>358.53224999999998</v>
       </c>
       <c r="H91">
         <v>47</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>22</v>
       </c>
@@ -3395,7 +3383,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>22</v>
       </c>
@@ -3421,7 +3409,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>22</v>
       </c>
@@ -3447,7 +3435,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>22</v>
       </c>
@@ -3473,7 +3461,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>22</v>
       </c>
@@ -3493,13 +3481,13 @@
         <v>164</v>
       </c>
       <c r="G96" s="1">
-        <v>93.86909999999999</v>
+        <v>93.869099999999989</v>
       </c>
       <c r="H96">
         <v>770</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>22</v>
       </c>
@@ -3519,13 +3507,13 @@
         <v>172</v>
       </c>
       <c r="G97" s="1">
-        <v>533.7354</v>
+        <v>533.73540000000003</v>
       </c>
       <c r="H97">
         <v>105</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>22</v>
       </c>
@@ -3551,7 +3539,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>22</v>
       </c>
@@ -3577,7 +3565,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>22</v>
       </c>
@@ -3597,13 +3585,13 @@
         <v>164</v>
       </c>
       <c r="G100" s="1">
-        <v>84.561</v>
+        <v>84.561000000000007</v>
       </c>
       <c r="H100">
         <v>996</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>8</v>
       </c>
@@ -3629,7 +3617,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>22</v>
       </c>
@@ -3649,13 +3637,13 @@
         <v>180</v>
       </c>
       <c r="G102" s="1">
-        <v>92.7828</v>
+        <v>92.782799999999995</v>
       </c>
       <c r="H102">
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>8</v>
       </c>
@@ -3675,13 +3663,28 @@
         <v>182</v>
       </c>
       <c r="G103" s="1">
-        <v>65.99804999999999</v>
+        <v>65.998049999999992</v>
       </c>
       <c r="H103">
         <v>2170</v>
       </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I103" s="1">
+        <f>G103*1.13</f>
+        <v>74.577796499999991</v>
+      </c>
+      <c r="J103">
+        <v>115</v>
+      </c>
+      <c r="K103">
+        <f>J103*0.92</f>
+        <v>105.80000000000001</v>
+      </c>
+      <c r="L103" s="1">
+        <f>K103/I103</f>
+        <v>1.418652802379325</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>8</v>
       </c>
@@ -3707,7 +3710,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>8</v>
       </c>
@@ -3733,7 +3736,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>8</v>
       </c>
@@ -3759,7 +3762,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>8</v>
       </c>
@@ -3785,7 +3788,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>8</v>
       </c>
@@ -3811,7 +3814,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>8</v>
       </c>
@@ -3831,13 +3834,13 @@
         <v>188</v>
       </c>
       <c r="G109" s="1">
-        <v>149.85615</v>
+        <v>149.85615000000001</v>
       </c>
       <c r="H109">
         <v>119</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>8</v>
       </c>
@@ -3857,13 +3860,13 @@
         <v>185</v>
       </c>
       <c r="G110" s="1">
-        <v>146.9274</v>
+        <v>146.92740000000001</v>
       </c>
       <c r="H110">
         <v>792</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>8</v>
       </c>
@@ -3889,7 +3892,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>8</v>
       </c>
@@ -3916,7 +3919,90 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H112">
+    <filterColumn colId="6">
+      <filters>
+        <filter val="R$ 66,00"/>
+        <filter val="R$ 76,99"/>
+        <filter val="R$ 79,67"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="7">
+      <filters>
+        <filter val="105"/>
+        <filter val="113"/>
+        <filter val="114"/>
+        <filter val="115"/>
+        <filter val="118"/>
+        <filter val="119"/>
+        <filter val="122"/>
+        <filter val="124"/>
+        <filter val="145"/>
+        <filter val="147"/>
+        <filter val="1489"/>
+        <filter val="150"/>
+        <filter val="154"/>
+        <filter val="172"/>
+        <filter val="173"/>
+        <filter val="174"/>
+        <filter val="175"/>
+        <filter val="215"/>
+        <filter val="2170"/>
+        <filter val="238"/>
+        <filter val="25"/>
+        <filter val="28"/>
+        <filter val="281"/>
+        <filter val="283"/>
+        <filter val="2836"/>
+        <filter val="29"/>
+        <filter val="290"/>
+        <filter val="30"/>
+        <filter val="33"/>
+        <filter val="330"/>
+        <filter val="335"/>
+        <filter val="343"/>
+        <filter val="37"/>
+        <filter val="38"/>
+        <filter val="41"/>
+        <filter val="43"/>
+        <filter val="443"/>
+        <filter val="45"/>
+        <filter val="46"/>
+        <filter val="47"/>
+        <filter val="49"/>
+        <filter val="50"/>
+        <filter val="513"/>
+        <filter val="52"/>
+        <filter val="57"/>
+        <filter val="58"/>
+        <filter val="60"/>
+        <filter val="61"/>
+        <filter val="63"/>
+        <filter val="64"/>
+        <filter val="66"/>
+        <filter val="68"/>
+        <filter val="69"/>
+        <filter val="697"/>
+        <filter val="73"/>
+        <filter val="76"/>
+        <filter val="77"/>
+        <filter val="770"/>
+        <filter val="78"/>
+        <filter val="792"/>
+        <filter val="80"/>
+        <filter val="84"/>
+        <filter val="85"/>
+        <filter val="86"/>
+        <filter val="87"/>
+        <filter val="88"/>
+        <filter val="89"/>
+        <filter val="90"/>
+        <filter val="94"/>
+        <filter val="996"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/analises/vinhos/tanyno-brancos-agosto-2026.xlsx
+++ b/analises/vinhos/tanyno-brancos-agosto-2026.xlsx
@@ -946,16 +946,18 @@
   <dimension ref="A1:L112"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="14.44140625" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="20" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="14" style="1" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="10" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="0" hidden="1" customWidth="1"/>
-    <col min="11" max="12" width="0" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1012,6 +1014,10 @@
       <c r="H2">
         <v>3</v>
       </c>
+      <c r="I2" s="1">
+        <f t="shared" ref="I2:I33" si="0">G2*1.13</f>
+        <v>821.77583249999986</v>
+      </c>
     </row>
     <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -1079,6 +1085,10 @@
       <c r="H4">
         <v>290</v>
       </c>
+      <c r="I4" s="1">
+        <f t="shared" ref="I4:I67" si="1">G4*1.13</f>
+        <v>306.98806049999996</v>
+      </c>
     </row>
     <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -1105,6 +1115,10 @@
       <c r="H5">
         <v>215</v>
       </c>
+      <c r="I5" s="1">
+        <f t="shared" si="1"/>
+        <v>306.98806049999996</v>
+      </c>
     </row>
     <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -1130,6 +1144,10 @@
       </c>
       <c r="H6">
         <v>283</v>
+      </c>
+      <c r="I6" s="1">
+        <f t="shared" si="1"/>
+        <v>306.98806049999996</v>
       </c>
     </row>
     <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -1158,7 +1176,7 @@
         <v>173</v>
       </c>
       <c r="I7" s="1">
-        <f>G7*1.13</f>
+        <f t="shared" si="1"/>
         <v>90.03009449999999</v>
       </c>
       <c r="J7">
@@ -1198,6 +1216,10 @@
       <c r="H8">
         <v>697</v>
       </c>
+      <c r="I8" s="1">
+        <f t="shared" si="1"/>
+        <v>179.20573949999996</v>
+      </c>
     </row>
     <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -1224,6 +1246,10 @@
       <c r="H9">
         <v>281</v>
       </c>
+      <c r="I9" s="1">
+        <f t="shared" si="1"/>
+        <v>121.87338149999998</v>
+      </c>
     </row>
     <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -1250,6 +1276,10 @@
       <c r="H10">
         <v>6</v>
       </c>
+      <c r="I10" s="1">
+        <f t="shared" si="1"/>
+        <v>170.75752049999997</v>
+      </c>
     </row>
     <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
@@ -1276,6 +1306,10 @@
       <c r="H11">
         <v>3</v>
       </c>
+      <c r="I11" s="1">
+        <f t="shared" si="1"/>
+        <v>1055.3293739999997</v>
+      </c>
     </row>
     <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -1302,6 +1336,10 @@
       <c r="H12">
         <v>4</v>
       </c>
+      <c r="I12" s="1">
+        <f t="shared" si="1"/>
+        <v>917.77503899999988</v>
+      </c>
     </row>
     <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -1328,6 +1366,10 @@
       <c r="H13">
         <v>21</v>
       </c>
+      <c r="I13" s="1">
+        <f t="shared" si="1"/>
+        <v>917.77503899999988</v>
+      </c>
     </row>
     <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -1353,6 +1395,10 @@
       </c>
       <c r="H14">
         <v>68</v>
+      </c>
+      <c r="I14" s="1">
+        <f t="shared" si="1"/>
+        <v>308.347959</v>
       </c>
     </row>
     <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -1380,6 +1426,10 @@
       <c r="H15">
         <v>1</v>
       </c>
+      <c r="I15" s="1">
+        <f t="shared" si="1"/>
+        <v>507.7475895</v>
+      </c>
     </row>
     <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -1406,8 +1456,12 @@
       <c r="H16">
         <v>41</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I16" s="1">
+        <f t="shared" si="1"/>
+        <v>477.20402849999994</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -1432,8 +1486,12 @@
       <c r="H17">
         <v>66</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I17" s="1">
+        <f t="shared" si="1"/>
+        <v>355.25843999999995</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>8</v>
       </c>
@@ -1458,8 +1516,12 @@
       <c r="H18">
         <v>20</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I18" s="1">
+        <f t="shared" si="1"/>
+        <v>402.99930149999994</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>8</v>
       </c>
@@ -1484,8 +1546,12 @@
       <c r="H19">
         <v>77</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I19" s="1">
+        <f t="shared" si="1"/>
+        <v>300.62180999999993</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -1510,8 +1576,12 @@
       <c r="H20">
         <v>38</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I20" s="1">
+        <f>G20*1.21</f>
+        <v>206.22265949999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -1536,8 +1606,12 @@
       <c r="H21">
         <v>443</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I21" s="1">
+        <f t="shared" si="1"/>
+        <v>170.88989999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -1562,8 +1636,12 @@
       <c r="H22">
         <v>90</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I22" s="1">
+        <f t="shared" si="1"/>
+        <v>404.29902749999997</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -1588,8 +1666,12 @@
       <c r="H23">
         <v>68</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I23" s="1">
+        <f t="shared" ref="I23:I24" si="2">G23*1.21</f>
+        <v>664.72432950000007</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>8</v>
       </c>
@@ -1614,8 +1696,12 @@
       <c r="H24">
         <v>33</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I24" s="1">
+        <f t="shared" si="2"/>
+        <v>5913.073617</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>8</v>
       </c>
@@ -1640,8 +1726,12 @@
       <c r="H25">
         <v>175</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I25" s="1">
+        <f t="shared" si="1"/>
+        <v>207.00543449999995</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>8</v>
       </c>
@@ -1666,8 +1756,12 @@
       <c r="H26">
         <v>45</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I26" s="1">
+        <f t="shared" si="1"/>
+        <v>447.98426249999994</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>8</v>
       </c>
@@ -1692,8 +1786,12 @@
       <c r="H27">
         <v>17</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I27" s="1">
+        <f t="shared" si="1"/>
+        <v>441.81056399999994</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>8</v>
       </c>
@@ -1718,8 +1816,12 @@
       <c r="H28">
         <v>50</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I28" s="1">
+        <f t="shared" ref="I28:I44" si="3">G28*1.21</f>
+        <v>344.82985349999996</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>8</v>
       </c>
@@ -1744,8 +1846,12 @@
       <c r="H29">
         <v>89</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I29" s="1">
+        <f t="shared" si="3"/>
+        <v>343.06440300000003</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>8</v>
       </c>
@@ -1770,8 +1876,12 @@
       <c r="H30">
         <v>63</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I30" s="1">
+        <f t="shared" si="3"/>
+        <v>266.3510685</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>8</v>
       </c>
@@ -1796,8 +1906,12 @@
       <c r="H31">
         <v>29</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I31" s="1">
+        <f t="shared" si="3"/>
+        <v>346.29891449999997</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>8</v>
       </c>
@@ -1822,8 +1936,12 @@
       <c r="H32">
         <v>80</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I32" s="1">
+        <f t="shared" si="3"/>
+        <v>353.21896499999997</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>8</v>
       </c>
@@ -1848,8 +1966,12 @@
       <c r="H33">
         <v>174</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I33" s="1">
+        <f t="shared" si="3"/>
+        <v>277.31747999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>8</v>
       </c>
@@ -1874,8 +1996,12 @@
       <c r="H34">
         <v>86</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I34" s="1">
+        <f t="shared" si="3"/>
+        <v>368.94049499999994</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>8</v>
       </c>
@@ -1900,8 +2026,12 @@
       <c r="H35">
         <v>335</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I35" s="1">
+        <f t="shared" si="3"/>
+        <v>345.55149749999993</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>8</v>
       </c>
@@ -1926,8 +2056,12 @@
       <c r="H36">
         <v>87</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I36" s="1">
+        <f t="shared" si="3"/>
+        <v>322.67795999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>8</v>
       </c>
@@ -1952,8 +2086,12 @@
       <c r="H37">
         <v>46</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I37" s="1">
+        <f t="shared" si="3"/>
+        <v>322.67795999999998</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>8</v>
       </c>
@@ -1978,8 +2116,12 @@
       <c r="H38">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I38" s="1">
+        <f t="shared" si="3"/>
+        <v>1694.9742314999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>8</v>
       </c>
@@ -2004,8 +2146,12 @@
       <c r="H39">
         <v>17</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I39" s="1">
+        <f t="shared" si="3"/>
+        <v>705.1235069999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>8</v>
       </c>
@@ -2030,8 +2176,12 @@
       <c r="H40">
         <v>238</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I40" s="1">
+        <f t="shared" si="3"/>
+        <v>344.82985349999996</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>8</v>
       </c>
@@ -2056,8 +2206,12 @@
       <c r="H41">
         <v>1489</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I41" s="1">
+        <f t="shared" si="3"/>
+        <v>143.49117749999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>8</v>
       </c>
@@ -2082,8 +2236,12 @@
       <c r="H42">
         <v>10</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I42" s="1">
+        <f t="shared" si="3"/>
+        <v>851.34662249999985</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>8</v>
       </c>
@@ -2108,8 +2266,12 @@
       <c r="H43">
         <v>124</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I43" s="1">
+        <f t="shared" si="3"/>
+        <v>908.56268249999982</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>8</v>
       </c>
@@ -2134,8 +2296,12 @@
       <c r="H44">
         <v>45</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I44" s="1">
+        <f t="shared" si="3"/>
+        <v>1922.0085884999996</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>22</v>
       </c>
@@ -2160,8 +2326,12 @@
       <c r="H45">
         <v>88</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I45" s="1">
+        <f t="shared" si="1"/>
+        <v>545.53591949999998</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>22</v>
       </c>
@@ -2186,8 +2356,12 @@
       <c r="H46">
         <v>122</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I46" s="1">
+        <f t="shared" si="1"/>
+        <v>136.15833299999997</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>8</v>
       </c>
@@ -2212,8 +2386,12 @@
       <c r="H47">
         <v>16</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I47" s="1">
+        <f t="shared" ref="I47:I48" si="4">G47*1.21</f>
+        <v>7769.038892999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>8</v>
       </c>
@@ -2238,8 +2416,12 @@
       <c r="H48">
         <v>25</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I48" s="1">
+        <f t="shared" si="4"/>
+        <v>7742.0545620000003</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>8</v>
       </c>
@@ -2264,8 +2446,12 @@
       <c r="H49">
         <v>37</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I49" s="1">
+        <f t="shared" si="1"/>
+        <v>146.19510600000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>8</v>
       </c>
@@ -2290,8 +2476,12 @@
       <c r="H50">
         <v>343</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I50" s="1">
+        <f t="shared" si="1"/>
+        <v>159.52933199999998</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>8</v>
       </c>
@@ -2316,8 +2506,12 @@
       <c r="H51">
         <v>113</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I51" s="1">
+        <f t="shared" si="1"/>
+        <v>366.47459399999991</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>8</v>
       </c>
@@ -2342,8 +2536,12 @@
       <c r="H52">
         <v>150</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I52" s="1">
+        <f t="shared" si="1"/>
+        <v>218.01700199999996</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>8</v>
       </c>
@@ -2368,8 +2566,12 @@
       <c r="H53">
         <v>4</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I53" s="1">
+        <f t="shared" ref="I53:I54" si="5">G53*1.21</f>
+        <v>2887.9548555000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>8</v>
       </c>
@@ -2394,8 +2596,12 @@
       <c r="H54">
         <v>33</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I54" s="1">
+        <f t="shared" si="5"/>
+        <v>3699.1213709999997</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>8</v>
       </c>
@@ -2420,8 +2626,12 @@
       <c r="H55">
         <v>16</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I55" s="1">
+        <f t="shared" si="1"/>
+        <v>245.85280049999994</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>8</v>
       </c>
@@ -2446,8 +2656,12 @@
       <c r="H56">
         <v>80</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I56" s="1">
+        <f t="shared" si="1"/>
+        <v>166.89444599999999</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>8</v>
       </c>
@@ -2472,8 +2686,12 @@
       <c r="H57">
         <v>69</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I57" s="1">
+        <f t="shared" si="1"/>
+        <v>383.63579099999987</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>8</v>
       </c>
@@ -2498,8 +2716,12 @@
       <c r="H58">
         <v>94</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I58" s="1">
+        <f t="shared" si="1"/>
+        <v>356.18509649999999</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>8</v>
       </c>
@@ -2524,8 +2746,12 @@
       <c r="H59">
         <v>330</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I59" s="1">
+        <f t="shared" ref="I59:I60" si="6">G59*1.21</f>
+        <v>302.43326849999994</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>8</v>
       </c>
@@ -2550,8 +2776,12 @@
       <c r="H60">
         <v>172</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I60" s="1">
+        <f t="shared" si="6"/>
+        <v>445.34455349999996</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>8</v>
       </c>
@@ -2576,8 +2806,12 @@
       <c r="H61">
         <v>147</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I61" s="1">
+        <f t="shared" si="1"/>
+        <v>288.32255099999998</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>8</v>
       </c>
@@ -2602,8 +2836,12 @@
       <c r="H62">
         <v>2</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I62" s="1">
+        <f t="shared" ref="I62:I79" si="7">G62*1.21</f>
+        <v>229.17351599999998</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>8</v>
       </c>
@@ -2628,8 +2866,12 @@
       <c r="H63">
         <v>6</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I63" s="1">
+        <f t="shared" si="7"/>
+        <v>276.51851700000003</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>8</v>
       </c>
@@ -2654,8 +2896,12 @@
       <c r="H64">
         <v>115</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I64" s="1">
+        <f t="shared" si="7"/>
+        <v>304.73995199999996</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>8</v>
       </c>
@@ -2680,8 +2926,12 @@
       <c r="H65">
         <v>513</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I65" s="1">
+        <f t="shared" si="7"/>
+        <v>225.42354450000002</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>8</v>
       </c>
@@ -2706,8 +2956,12 @@
       <c r="H66">
         <v>38</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I66" s="1">
+        <f t="shared" si="7"/>
+        <v>187.85939699999997</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>8</v>
       </c>
@@ -2732,8 +2986,12 @@
       <c r="H67">
         <v>30</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I67" s="1">
+        <f t="shared" si="7"/>
+        <v>382.02029249999998</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>8</v>
       </c>
@@ -2758,8 +3016,12 @@
       <c r="H68">
         <v>66</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I68" s="1">
+        <f t="shared" si="7"/>
+        <v>908.56268249999982</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>8</v>
       </c>
@@ -2784,8 +3046,12 @@
       <c r="H69">
         <v>58</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I69" s="1">
+        <f t="shared" si="7"/>
+        <v>1809.4063514999998</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>8</v>
       </c>
@@ -2810,8 +3076,12 @@
       <c r="H70">
         <v>7</v>
       </c>
-    </row>
-    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I70" s="1">
+        <f t="shared" si="7"/>
+        <v>1470.0146009999999</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>8</v>
       </c>
@@ -2836,8 +3106,12 @@
       <c r="H71">
         <v>4</v>
       </c>
-    </row>
-    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I71" s="1">
+        <f t="shared" si="7"/>
+        <v>3022.270845</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>8</v>
       </c>
@@ -2862,8 +3136,12 @@
       <c r="H72">
         <v>2</v>
       </c>
-    </row>
-    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I72" s="1">
+        <f t="shared" si="7"/>
+        <v>835.05808649999994</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>8</v>
       </c>
@@ -2888,8 +3166,12 @@
       <c r="H73">
         <v>11</v>
       </c>
-    </row>
-    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I73" s="1">
+        <f t="shared" si="7"/>
+        <v>920.48269499999992</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>8</v>
       </c>
@@ -2914,8 +3196,12 @@
       <c r="H74">
         <v>10</v>
       </c>
-    </row>
-    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I74" s="1">
+        <f t="shared" si="7"/>
+        <v>920.48269499999992</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>8</v>
       </c>
@@ -2940,8 +3226,12 @@
       <c r="H75">
         <v>64</v>
       </c>
-    </row>
-    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I75" s="1">
+        <f t="shared" si="7"/>
+        <v>639.73740599999985</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>8</v>
       </c>
@@ -2966,8 +3256,12 @@
       <c r="H76">
         <v>33</v>
       </c>
-    </row>
-    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I76" s="1">
+        <f t="shared" si="7"/>
+        <v>641.83790549999992</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>8</v>
       </c>
@@ -2992,8 +3286,12 @@
       <c r="H77">
         <v>49</v>
       </c>
-    </row>
-    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I77" s="1">
+        <f t="shared" si="7"/>
+        <v>639.73740599999985</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>8</v>
       </c>
@@ -3018,8 +3316,12 @@
       <c r="H78">
         <v>61</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I78" s="1">
+        <f t="shared" si="7"/>
+        <v>1922.0085884999996</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>8</v>
       </c>
@@ -3044,8 +3346,12 @@
       <c r="H79">
         <v>28</v>
       </c>
-    </row>
-    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I79" s="1">
+        <f t="shared" si="7"/>
+        <v>245.92596599999999</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>8</v>
       </c>
@@ -3070,8 +3376,12 @@
       <c r="H80">
         <v>114</v>
       </c>
-    </row>
-    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I80" s="1">
+        <f t="shared" ref="I68:I112" si="8">G80*1.13</f>
+        <v>276.09549899999996</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>8</v>
       </c>
@@ -3096,8 +3406,12 @@
       <c r="H81">
         <v>76</v>
       </c>
-    </row>
-    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I81" s="1">
+        <f>G81*1.21</f>
+        <v>456.86508449999991</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>8</v>
       </c>
@@ -3122,8 +3436,12 @@
       <c r="H82">
         <v>57</v>
       </c>
-    </row>
-    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I82" s="1">
+        <f t="shared" si="8"/>
+        <v>286.63772099999994</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>8</v>
       </c>
@@ -3148,8 +3466,12 @@
       <c r="H83">
         <v>78</v>
       </c>
-    </row>
-    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I83" s="1">
+        <f t="shared" si="8"/>
+        <v>393.79290899999995</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>8</v>
       </c>
@@ -3174,8 +3496,12 @@
       <c r="H84">
         <v>63</v>
       </c>
-    </row>
-    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I84" s="1">
+        <f t="shared" si="8"/>
+        <v>401.14598849999993</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>8</v>
       </c>
@@ -3200,8 +3526,12 @@
       <c r="H85">
         <v>85</v>
       </c>
-    </row>
-    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I85" s="1">
+        <f t="shared" si="8"/>
+        <v>393.79290899999995</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>8</v>
       </c>
@@ -3226,8 +3556,12 @@
       <c r="H86">
         <v>52</v>
       </c>
-    </row>
-    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I86" s="1">
+        <f t="shared" si="8"/>
+        <v>368.58063149999992</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>8</v>
       </c>
@@ -3252,8 +3586,12 @@
       <c r="H87">
         <v>115</v>
       </c>
-    </row>
-    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I87" s="1">
+        <f t="shared" si="8"/>
+        <v>313.95603599999998</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>8</v>
       </c>
@@ -3278,8 +3616,12 @@
       <c r="H88">
         <v>118</v>
       </c>
-    </row>
-    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I88" s="1">
+        <f t="shared" si="8"/>
+        <v>322.70511749999991</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>8</v>
       </c>
@@ -3304,8 +3646,12 @@
       <c r="H89">
         <v>73</v>
       </c>
-    </row>
-    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I89" s="1">
+        <f t="shared" si="8"/>
+        <v>196.715937</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>22</v>
       </c>
@@ -3330,8 +3676,12 @@
       <c r="H90">
         <v>30</v>
       </c>
-    </row>
-    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I90" s="1">
+        <f t="shared" si="8"/>
+        <v>209.96592149999995</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>8</v>
       </c>
@@ -3356,8 +3706,12 @@
       <c r="H91">
         <v>47</v>
       </c>
-    </row>
-    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I91" s="1">
+        <f t="shared" si="8"/>
+        <v>405.14144249999993</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>22</v>
       </c>
@@ -3382,8 +3736,12 @@
       <c r="H92">
         <v>154</v>
       </c>
-    </row>
-    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I92" s="1">
+        <f t="shared" si="8"/>
+        <v>177.15987449999997</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>22</v>
       </c>
@@ -3408,8 +3766,12 @@
       <c r="H93">
         <v>60</v>
       </c>
-    </row>
-    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I93" s="1">
+        <f t="shared" si="8"/>
+        <v>251.19611849999995</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>22</v>
       </c>
@@ -3434,8 +3796,12 @@
       <c r="H94">
         <v>113</v>
       </c>
-    </row>
-    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I94" s="1">
+        <f t="shared" si="8"/>
+        <v>251.19611849999995</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>22</v>
       </c>
@@ -3460,8 +3826,12 @@
       <c r="H95">
         <v>23</v>
       </c>
-    </row>
-    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I95" s="1">
+        <f t="shared" si="8"/>
+        <v>260.48675249999997</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>22</v>
       </c>
@@ -3485,6 +3855,10 @@
       </c>
       <c r="H96">
         <v>770</v>
+      </c>
+      <c r="I96" s="1">
+        <f t="shared" si="8"/>
+        <v>106.07208299999998</v>
       </c>
     </row>
     <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3512,6 +3886,10 @@
       <c r="H97">
         <v>105</v>
       </c>
+      <c r="I97" s="1">
+        <f t="shared" si="8"/>
+        <v>603.12100199999998</v>
+      </c>
     </row>
     <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
@@ -3538,6 +3916,10 @@
       <c r="H98">
         <v>6</v>
       </c>
+      <c r="I98" s="1">
+        <f t="shared" si="8"/>
+        <v>534.65673149999986</v>
+      </c>
     </row>
     <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
@@ -3564,6 +3946,10 @@
       <c r="H99">
         <v>3</v>
       </c>
+      <c r="I99" s="1">
+        <f t="shared" si="8"/>
+        <v>1338.9705044999996</v>
+      </c>
     </row>
     <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
@@ -3590,6 +3976,10 @@
       <c r="H100">
         <v>996</v>
       </c>
+      <c r="I100" s="1">
+        <f t="shared" si="8"/>
+        <v>95.553929999999994</v>
+      </c>
     </row>
     <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
@@ -3615,6 +4005,10 @@
       </c>
       <c r="H101">
         <v>43</v>
+      </c>
+      <c r="I101" s="1">
+        <f t="shared" si="8"/>
+        <v>211.22954399999998</v>
       </c>
     </row>
     <row r="102" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3642,8 +4036,12 @@
       <c r="H102">
         <v>5</v>
       </c>
-    </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I102" s="1">
+        <f t="shared" si="8"/>
+        <v>104.84456399999998</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>8</v>
       </c>
@@ -3669,7 +4067,7 @@
         <v>2170</v>
       </c>
       <c r="I103" s="1">
-        <f>G103*1.13</f>
+        <f t="shared" si="8"/>
         <v>74.577796499999991</v>
       </c>
       <c r="J103">
@@ -3709,6 +4107,10 @@
       <c r="H104">
         <v>90</v>
       </c>
+      <c r="I104" s="1">
+        <f t="shared" si="8"/>
+        <v>194.57379599999999</v>
+      </c>
     </row>
     <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
@@ -3735,6 +4137,10 @@
       <c r="H105">
         <v>85</v>
       </c>
+      <c r="I105" s="1">
+        <f t="shared" si="8"/>
+        <v>279.99467699999997</v>
+      </c>
     </row>
     <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
@@ -3761,6 +4167,10 @@
       <c r="H106">
         <v>13</v>
       </c>
+      <c r="I106" s="1">
+        <f t="shared" si="8"/>
+        <v>195.30790049999996</v>
+      </c>
     </row>
     <row r="107" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
@@ -3787,6 +4197,10 @@
       <c r="H107">
         <v>85</v>
       </c>
+      <c r="I107" s="1">
+        <f t="shared" si="8"/>
+        <v>279.99467699999997</v>
+      </c>
     </row>
     <row r="108" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
@@ -3813,6 +4227,10 @@
       <c r="H108">
         <v>84</v>
       </c>
+      <c r="I108" s="1">
+        <f t="shared" si="8"/>
+        <v>279.99467699999997</v>
+      </c>
     </row>
     <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
@@ -3839,6 +4257,10 @@
       <c r="H109">
         <v>119</v>
       </c>
+      <c r="I109" s="1">
+        <f t="shared" si="8"/>
+        <v>169.33744949999999</v>
+      </c>
     </row>
     <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
@@ -3865,6 +4287,10 @@
       <c r="H110">
         <v>792</v>
       </c>
+      <c r="I110" s="1">
+        <f t="shared" si="8"/>
+        <v>166.027962</v>
+      </c>
     </row>
     <row r="111" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
@@ -3891,6 +4317,10 @@
       <c r="H111">
         <v>145</v>
       </c>
+      <c r="I111" s="1">
+        <f t="shared" si="8"/>
+        <v>372.92508599999996</v>
+      </c>
     </row>
     <row r="112" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
@@ -3917,14 +4347,54 @@
       <c r="H112">
         <v>60</v>
       </c>
+      <c r="I112" s="1">
+        <f t="shared" si="8"/>
+        <v>298.01032349999991</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H112">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="FRANÇA"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="5">
+      <filters>
+        <filter val="BORGONHA"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="6">
       <filters>
-        <filter val="R$ 66,00"/>
-        <filter val="R$ 76,99"/>
-        <filter val="R$ 79,67"/>
+        <filter val="R$ 118,59"/>
+        <filter val="R$ 155,26"/>
+        <filter val="R$ 170,43"/>
+        <filter val="R$ 186,30"/>
+        <filter val="R$ 189,40"/>
+        <filter val="R$ 203,24"/>
+        <filter val="R$ 220,12"/>
+        <filter val="R$ 228,53"/>
+        <filter val="R$ 229,19"/>
+        <filter val="R$ 249,94"/>
+        <filter val="R$ 251,85"/>
+        <filter val="R$ 266,68"/>
+        <filter val="R$ 283,52"/>
+        <filter val="R$ 284,98"/>
+        <filter val="R$ 285,58"/>
+        <filter val="R$ 286,20"/>
+        <filter val="R$ 291,92"/>
+        <filter val="R$ 304,91"/>
+        <filter val="R$ 315,72"/>
+        <filter val="R$ 368,05"/>
+        <filter val="R$ 377,57"/>
+        <filter val="R$ 528,71"/>
+        <filter val="R$ 530,44"/>
+        <filter val="R$ 549,36"/>
+        <filter val="R$ 582,75"/>
+        <filter val="R$ 690,13"/>
+        <filter val="R$ 703,59"/>
+        <filter val="R$ 750,88"/>
+        <filter val="R$ 760,73"/>
       </filters>
     </filterColumn>
     <filterColumn colId="7">
